--- a/.xlsx files/Skyscrapers.xlsx
+++ b/.xlsx files/Skyscrapers.xlsx
@@ -893,7 +893,7 @@
     <t>Harnuk</t>
   </si>
   <si>
-    <t>lasri</t>
+    <t>Lasri</t>
   </si>
   <si>
     <t>Rukara</t>
